--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-08-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_30-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C650AEDB-3C33-4948-8115-A3B5B1291C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B977E9-2E86-4FE3-9B20-5E51EDD1F66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33570" yWindow="2265" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33660" yWindow="2355" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="386">
   <si>
     <t>SKU</t>
   </si>
@@ -1025,9 +1025,6 @@
   </si>
   <si>
     <t>£1,713.00</t>
-  </si>
-  <si>
-    <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/thermaclass-cavity-wall-21?variant=40086149333185</t>
   </si>
   <si>
     <t>£1654.88</t>
@@ -1631,7 +1628,7 @@
         <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K2" t="s">
         <v>25</v>
@@ -1743,7 +1740,7 @@
         <v>51</v>
       </c>
       <c r="J4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K4" t="s">
         <v>52</v>
@@ -1911,7 +1908,7 @@
         <v>92</v>
       </c>
       <c r="J7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K7" t="s">
         <v>93</v>
@@ -2023,7 +2020,7 @@
         <v>119</v>
       </c>
       <c r="J9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K9" t="s">
         <v>120</v>
@@ -2191,7 +2188,7 @@
         <v>157</v>
       </c>
       <c r="J12" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="K12" t="s">
         <v>158</v>
@@ -2247,7 +2244,7 @@
         <v>170</v>
       </c>
       <c r="J13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K13" t="s">
         <v>171</v>
@@ -2527,7 +2524,7 @@
         <v>232</v>
       </c>
       <c r="J18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K18" t="s">
         <v>233</v>
@@ -2571,7 +2568,7 @@
         <v>242</v>
       </c>
       <c r="F19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G19" t="s">
         <v>243</v>
@@ -2627,7 +2624,7 @@
         <v>255</v>
       </c>
       <c r="F20" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G20" t="s">
         <v>256</v>
@@ -2639,7 +2636,7 @@
         <v>196</v>
       </c>
       <c r="J20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K20" t="s">
         <v>258</v>
@@ -2683,7 +2680,7 @@
         <v>266</v>
       </c>
       <c r="F21" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G21" t="s">
         <v>267</v>
@@ -2695,7 +2692,7 @@
         <v>269</v>
       </c>
       <c r="J21" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="K21" t="s">
         <v>270</v>
@@ -2739,7 +2736,7 @@
         <v>278</v>
       </c>
       <c r="F22" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G22" t="s">
         <v>279</v>
@@ -2763,7 +2760,7 @@
         <v>284</v>
       </c>
       <c r="N22" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="O22" t="s">
         <v>278</v>
@@ -2795,7 +2792,7 @@
         <v>290</v>
       </c>
       <c r="F23" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G23" t="s">
         <v>156</v>
@@ -2851,7 +2848,7 @@
         <v>302</v>
       </c>
       <c r="F24" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G24" t="s">
         <v>156</v>
@@ -2963,7 +2960,7 @@
         <v>321</v>
       </c>
       <c r="F26" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G26" t="s">
         <v>156</v>
@@ -3013,161 +3010,161 @@
         <v>334</v>
       </c>
       <c r="D27" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E27" t="s">
         <v>334</v>
       </c>
       <c r="F27" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G27" t="s">
         <v>156</v>
       </c>
       <c r="H27" t="s">
+        <v>335</v>
+      </c>
+      <c r="I27" t="s">
         <v>336</v>
-      </c>
-      <c r="I27" t="s">
-        <v>337</v>
       </c>
       <c r="J27" t="s">
         <v>156</v>
       </c>
       <c r="K27" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L27" t="s">
         <v>21</v>
       </c>
       <c r="M27" t="s">
+        <v>338</v>
+      </c>
+      <c r="N27" t="s">
+        <v>383</v>
+      </c>
+      <c r="O27" t="s">
         <v>339</v>
       </c>
-      <c r="N27" t="s">
-        <v>384</v>
-      </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>340</v>
       </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>341</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
         <v>342</v>
-      </c>
-      <c r="R27" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>343</v>
+      </c>
+      <c r="B28" t="s">
         <v>344</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>345</v>
       </c>
-      <c r="C28" t="s">
-        <v>346</v>
-      </c>
       <c r="D28" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E28" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F28" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G28" t="s">
         <v>156</v>
       </c>
       <c r="H28" t="s">
+        <v>346</v>
+      </c>
+      <c r="I28" t="s">
         <v>347</v>
-      </c>
-      <c r="I28" t="s">
-        <v>348</v>
       </c>
       <c r="J28" t="s">
         <v>156</v>
       </c>
       <c r="K28" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L28" t="s">
         <v>21</v>
       </c>
       <c r="M28" t="s">
+        <v>349</v>
+      </c>
+      <c r="N28" t="s">
+        <v>384</v>
+      </c>
+      <c r="O28" t="s">
         <v>350</v>
       </c>
-      <c r="N28" t="s">
-        <v>385</v>
-      </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>351</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>352</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" t="s">
         <v>353</v>
-      </c>
-      <c r="R28" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>354</v>
+      </c>
+      <c r="B29" t="s">
         <v>355</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>356</v>
       </c>
-      <c r="C29" t="s">
-        <v>357</v>
-      </c>
       <c r="D29" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E29" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F29" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G29" t="s">
         <v>156</v>
       </c>
       <c r="H29" t="s">
+        <v>357</v>
+      </c>
+      <c r="I29" t="s">
         <v>358</v>
-      </c>
-      <c r="I29" t="s">
-        <v>359</v>
       </c>
       <c r="J29" t="s">
         <v>156</v>
       </c>
       <c r="K29" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L29" t="s">
         <v>156</v>
       </c>
       <c r="M29" t="s">
+        <v>360</v>
+      </c>
+      <c r="N29" t="s">
+        <v>385</v>
+      </c>
+      <c r="O29" t="s">
         <v>361</v>
       </c>
-      <c r="N29" t="s">
-        <v>386</v>
-      </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>362</v>
-      </c>
-      <c r="P29" t="s">
-        <v>363</v>
       </c>
       <c r="Q29" t="s">
         <v>156</v>
       </c>
       <c r="R29" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
